--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="205">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -587,6 +587,10 @@
   </si>
   <si>
     <t>fr-lm-procedure.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>localisation anatomique</t>
@@ -3836,13 +3840,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3872,7 +3876,7 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>73</v>
@@ -3910,10 +3914,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3939,10 +3943,10 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3972,7 +3976,7 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -3993,7 +3997,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4010,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4039,10 +4043,10 @@
         <v>131</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4093,7 +4097,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4110,10 +4114,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4136,13 +4140,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4193,7 +4197,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4210,10 +4214,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4239,10 +4243,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4293,7 +4297,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4310,10 +4314,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4339,10 +4343,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4372,7 +4376,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4393,7 +4397,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4410,10 +4414,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4439,10 +4443,10 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4493,7 +4497,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4510,10 +4514,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4539,10 +4543,10 @@
         <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4593,7 +4597,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4610,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4639,10 +4643,10 @@
         <v>150</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4693,7 +4697,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-procedure.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-procedure.header.langue</t>
+    <t>fr-lm-procedure.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-procedure.code</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="206">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -423,6 +423,9 @@
   </si>
   <si>
     <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>Statut</t>
   </si>
   <si>
     <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
@@ -2642,7 +2645,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2672,10 +2675,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2693,10 +2696,10 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2710,10 +2713,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2739,10 +2742,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2793,7 +2796,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2810,10 +2813,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2839,10 +2842,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2893,7 +2896,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2910,10 +2913,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2939,10 +2942,10 @@
         <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2972,7 +2975,7 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2993,7 +2996,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3010,10 +3013,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3036,13 +3039,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3093,7 +3096,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3105,15 +3108,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3136,13 +3139,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3193,7 +3196,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3210,14 +3213,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3236,16 +3239,16 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3283,19 +3286,19 @@
         <v>73</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3307,15 +3310,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3338,16 +3341,16 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3397,7 +3400,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3414,10 +3417,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3440,13 +3443,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3497,7 +3500,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3509,15 +3512,15 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3543,10 +3546,10 @@
         <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3597,7 +3600,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3614,10 +3617,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3643,10 +3646,10 @@
         <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3697,7 +3700,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3714,10 +3717,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3743,10 +3746,10 @@
         <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3776,7 +3779,7 @@
         <v>73</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>73</v>
@@ -3797,7 +3800,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3814,10 +3817,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3840,13 +3843,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3876,7 +3879,7 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>73</v>
@@ -3897,7 +3900,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3914,10 +3917,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3943,10 +3946,10 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3976,7 +3979,7 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -3997,7 +4000,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4014,10 +4017,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4043,10 +4046,10 @@
         <v>131</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4097,7 +4100,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4114,10 +4117,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4140,13 +4143,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4197,7 +4200,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4214,10 +4217,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4243,10 +4246,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4297,7 +4300,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4314,10 +4317,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4343,10 +4346,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4376,7 +4379,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4397,7 +4400,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4414,10 +4417,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4443,10 +4446,10 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4497,7 +4500,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4514,10 +4517,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4543,10 +4546,10 @@
         <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4597,7 +4600,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4614,10 +4617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4640,13 +4643,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4697,7 +4700,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
